--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile for body height.
+    <t>French profile for body height.
 Profil français de la mesure de la taille. Profil basé sur le profil bodyheight d'HL7</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodyheight</t>
+    <t>http://hl7.org/fhir/StructureDefinition/bodyheight|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,6 +488,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-height|2.2.0</t>
+  </si>
+  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -510,7 +513,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -534,7 +537,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -577,7 +580,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -653,14 +656,15 @@
     <t>bodyposition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Observation Height Body Position Extension</t>
   </si>
   <si>
-    <t>Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height. | Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing)</t>
+    <t>Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing).
+Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -673,7 +677,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -734,7 +738,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -763,7 +767,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -843,7 +847,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1098,7 +1102,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1192,7 +1196,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1223,7 +1227,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1246,7 +1250,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -1341,7 +1345,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1585,7 +1589,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1617,7 +1621,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1673,7 +1677,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1703,7 +1707,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://models.opencimi.org/ig/vital-signs-fhir-profiles/ValueSet-heightLengthMeasMethodVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-height-meas-method|2.2.0</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1715,7 +1719,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1743,7 +1747,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1823,7 +1827,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1873,7 +1877,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1906,7 +1910,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1943,7 +1947,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1965,7 +1969,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2414,17 +2418,17 @@
   <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.29296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.76953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.3828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.60546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="226.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="222.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2433,28 +2437,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.80859375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.453125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3711,7 +3715,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3785,10 +3789,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3811,16 +3815,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3846,13 +3850,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -3870,7 +3874,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3905,10 +3909,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3931,16 +3935,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3966,13 +3970,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -3990,7 +3994,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4025,10 +4029,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4054,13 +4058,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4110,7 +4114,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4145,10 +4149,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4171,16 +4175,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4206,13 +4210,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -4230,7 +4234,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4265,14 +4269,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4291,16 +4295,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4350,7 +4354,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4374,7 +4378,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4385,14 +4389,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4411,16 +4415,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4470,7 +4474,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4494,7 +4498,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4505,10 +4509,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4534,10 +4538,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4586,7 +4590,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4621,13 +4625,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4649,13 +4653,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4706,7 +4710,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4715,7 +4719,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -4739,15 +4743,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>83</v>
@@ -4769,13 +4773,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4826,7 +4830,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4861,10 +4865,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4890,16 +4894,16 @@
         <v>115</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4948,7 +4952,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4972,7 +4976,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4983,10 +4987,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5009,17 +5013,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5068,7 +5072,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5083,19 +5087,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -5103,14 +5107,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5129,17 +5133,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5188,7 +5192,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5203,16 +5207,16 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5223,14 +5227,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5249,16 +5253,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5308,7 +5312,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5323,16 +5327,16 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5341,12 +5345,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5369,19 +5373,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5406,11 +5410,11 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5428,7 +5432,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5443,19 +5447,19 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5463,10 +5467,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5489,19 +5493,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5526,19 +5530,19 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5548,7 +5552,7 @@
         <v>121</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5572,24 +5576,24 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>83</v>
@@ -5611,19 +5615,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5648,13 +5652,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5672,7 +5676,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5696,10 +5700,10 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5707,10 +5711,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5825,10 +5829,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5943,12 +5947,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5971,19 +5975,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -6032,7 +6036,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6053,10 +6057,10 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -6067,10 +6071,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6185,10 +6189,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6303,12 +6307,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6334,23 +6338,23 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -6392,7 +6396,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6413,10 +6417,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6427,10 +6431,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6456,13 +6460,13 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6512,7 +6516,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6533,10 +6537,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6545,12 +6549,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6573,24 +6577,24 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6632,7 +6636,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6653,10 +6657,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6667,10 +6671,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6696,14 +6700,14 @@
         <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6752,7 +6756,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6773,10 +6777,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6787,10 +6791,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6813,19 +6817,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6874,7 +6878,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6895,10 +6899,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6909,10 +6913,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6938,16 +6942,16 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6996,7 +7000,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7017,10 +7021,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7029,16 +7033,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7057,19 +7061,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7094,13 +7098,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -7118,7 +7122,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>94</v>
@@ -7133,30 +7137,30 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7271,10 +7275,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7391,10 +7395,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7417,19 +7421,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7466,7 +7470,7 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7476,7 +7480,7 @@
         <v>121</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7497,10 +7501,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7511,13 +7515,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -7539,19 +7543,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7600,7 +7604,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7621,10 +7625,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7635,10 +7639,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7753,10 +7757,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7873,10 +7877,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7902,23 +7906,23 @@
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7960,7 +7964,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7981,10 +7985,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7995,10 +7999,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8024,13 +8028,13 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8080,7 +8084,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8101,10 +8105,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8115,10 +8119,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8141,24 +8145,24 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8200,7 +8204,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8221,10 +8225,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8235,10 +8239,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8264,14 +8268,14 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8320,7 +8324,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8341,10 +8345,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8355,10 +8359,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8381,19 +8385,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8442,7 +8446,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8463,10 +8467,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8477,10 +8481,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8506,16 +8510,16 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8564,7 +8568,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8585,10 +8589,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8597,12 +8601,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8625,19 +8629,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8686,7 +8690,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8701,19 +8705,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8721,10 +8725,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8747,16 +8751,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8806,7 +8810,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8827,13 +8831,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8841,14 +8845,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8867,19 +8871,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8928,7 +8932,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8943,34 +8947,34 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8989,19 +8993,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9050,7 +9054,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9059,25 +9063,25 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9085,10 +9089,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9114,13 +9118,13 @@
         <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9170,7 +9174,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9191,13 +9195,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9205,10 +9209,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9231,17 +9235,17 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9290,7 +9294,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9305,19 +9309,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9325,10 +9329,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9351,19 +9355,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9400,17 +9404,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9419,7 +9423,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9428,30 +9432,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9473,19 +9477,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9534,7 +9538,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9543,7 +9547,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9552,27 +9556,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9687,10 +9691,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9805,12 +9809,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9833,19 +9837,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9894,7 +9898,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9915,10 +9919,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9929,10 +9933,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9955,23 +9959,23 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>83</v>
@@ -9992,13 +9996,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10016,7 +10020,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10037,10 +10041,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10049,12 +10053,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10080,14 +10084,14 @@
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10136,7 +10140,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10157,10 +10161,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10169,12 +10173,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10200,21 +10204,21 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>83</v>
@@ -10256,7 +10260,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10265,7 +10269,7 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
@@ -10277,10 +10281,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10289,12 +10293,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10317,19 +10321,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10354,13 +10358,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10378,7 +10382,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10399,10 +10403,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10411,12 +10415,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10439,19 +10443,19 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10476,13 +10480,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10500,7 +10504,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10509,7 +10513,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10521,10 +10525,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10535,14 +10539,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10561,19 +10565,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10598,13 +10602,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10622,7 +10626,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10640,27 +10644,27 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10683,19 +10687,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10744,7 +10748,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10765,10 +10769,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10779,10 +10783,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10805,16 +10809,16 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10840,13 +10844,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10864,7 +10868,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10882,27 +10886,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10925,19 +10929,19 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10962,11 +10966,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10984,7 +10988,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11005,10 +11009,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11019,10 +11023,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11045,16 +11049,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11104,7 +11108,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11122,27 +11126,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11165,16 +11169,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11224,7 +11228,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11242,27 +11246,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11285,19 +11289,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11346,7 +11350,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11358,7 +11362,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11367,10 +11371,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11381,10 +11385,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11499,10 +11503,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11619,14 +11623,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11648,16 +11652,16 @@
         <v>115</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11706,7 +11710,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11730,7 +11734,7 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11741,10 +11745,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11767,13 +11771,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11824,7 +11828,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11833,7 +11837,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11845,10 +11849,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11859,10 +11863,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11885,13 +11889,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11942,7 +11946,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11951,7 +11955,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11963,10 +11967,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11977,10 +11981,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12003,19 +12007,19 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12040,13 +12044,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12064,7 +12068,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12082,13 +12086,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12099,10 +12103,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12125,19 +12129,19 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12162,13 +12166,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12186,7 +12190,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12204,13 +12208,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12221,10 +12225,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12247,17 +12251,17 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12306,7 +12310,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12330,7 +12334,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12341,10 +12345,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12370,10 +12374,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12424,7 +12428,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12445,10 +12449,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12459,10 +12463,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12485,16 +12489,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12544,7 +12548,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12565,10 +12569,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12579,10 +12583,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12605,16 +12609,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12664,7 +12668,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12685,10 +12689,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12697,12 +12701,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12725,19 +12729,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12786,7 +12790,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12798,7 +12802,7 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12807,10 +12811,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12821,10 +12825,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12939,10 +12943,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13059,14 +13063,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13088,16 +13092,16 @@
         <v>115</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13146,7 +13150,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13170,7 +13174,7 @@
         <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13179,12 +13183,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13207,19 +13211,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13244,13 +13248,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13268,7 +13272,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13286,27 +13290,27 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13329,19 +13333,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13366,13 +13370,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13390,7 +13394,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13399,7 +13403,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13408,27 +13412,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13451,19 +13455,19 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13488,13 +13492,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13512,7 +13516,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13521,7 +13525,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13533,10 +13537,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13547,14 +13551,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13573,19 +13577,19 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13610,13 +13614,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13634,7 +13638,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13652,27 +13656,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13698,16 +13702,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13756,7 +13760,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13777,10 +13781,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13791,12 +13795,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP94">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="664">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile for body height.
+    <t>French profile for body height.
 Profil français de la mesure de la taille. Profil basé sur le profil bodyheight d'HL7</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodyheight|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/bodyheight</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
+    <t xml:space="preserve">canonical(StructureDefinition)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,9 +488,6 @@
     <t>fr-canonical</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-height|2.2.0</t>
-  </si>
-  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -513,7 +510,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -537,7 +534,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -580,7 +577,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -656,15 +653,14 @@
     <t>bodyposition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position|2.2.0}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position}
 </t>
   </si>
   <si>
     <t>FR Core Observation Height Body Position Extension</t>
   </si>
   <si>
-    <t>Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing).
-Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height.</t>
+    <t>Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height. | Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing)</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -677,7 +673,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
+    <t xml:space="preserve">Extension {workflow-supportingInfo}
 </t>
   </si>
   <si>
@@ -738,7 +734,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
+    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
 </t>
   </si>
   <si>
@@ -767,7 +763,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
+    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
 </t>
   </si>
   <si>
@@ -847,7 +843,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1102,7 +1098,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1196,7 +1192,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
 </t>
   </si>
   <si>
@@ -1227,7 +1223,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource|4.0.1)
+    <t xml:space="preserve">Reference(Resource)
 </t>
   </si>
   <si>
@@ -1250,7 +1246,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
 </t>
   </si>
   <si>
@@ -1345,7 +1341,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
+    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
 </t>
   </si>
   <si>
@@ -1589,7 +1585,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
   </si>
   <si>
     <t>obs-6
@@ -1621,7 +1617,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1677,7 +1673,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1707,7 +1703,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-height-meas-method|2.2.0</t>
+    <t>http://models.opencimi.org/ig/vital-signs-fhir-profiles/ValueSet-heightLengthMeasMethodVS</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1719,7 +1715,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen|4.0.1)
+    <t xml:space="preserve">Reference(Specimen)
 </t>
   </si>
   <si>
@@ -1747,7 +1743,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
+    <t xml:space="preserve">Reference(Device|DeviceMetric)
 </t>
   </si>
   <si>
@@ -1827,7 +1823,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
+    <t xml:space="preserve">Quantity {SimpleQuantity}
 </t>
   </si>
   <si>
@@ -1877,7 +1873,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1910,7 +1906,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1947,7 +1943,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
 </t>
   </si>
   <si>
@@ -1969,7 +1965,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
+    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
 </t>
   </si>
   <si>
@@ -2418,17 +2414,17 @@
   <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="43.3828125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.60546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="50.29296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="15.76953125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="222.875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="226.43359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2437,28 +2433,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="59.453125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="85.80859375" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3715,7 +3711,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>151</v>
+        <v>3</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3789,10 +3785,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3815,16 +3811,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3850,31 +3846,31 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="Y12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="Y12" t="s" s="2">
+      <c r="Z12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="Z12" t="s" s="2">
+      <c r="AA12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE12" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF12" t="s" s="2">
         <v>159</v>
-      </c>
-      <c r="AA12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE12" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF12" t="s" s="2">
-        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3909,10 +3905,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3935,16 +3931,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="M13" t="s" s="2">
+      <c r="N13" t="s" s="2">
         <v>163</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3970,31 +3966,31 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="Y13" t="s" s="2">
         <v>165</v>
       </c>
-      <c r="Y13" t="s" s="2">
+      <c r="Z13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="Z13" t="s" s="2">
+      <c r="AA13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AA13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF13" t="s" s="2">
-        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4029,10 +4025,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4058,13 +4054,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
-      <c r="M14" t="s" s="2">
+      <c r="N14" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4114,7 +4110,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4149,10 +4145,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4175,16 +4171,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>175</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="M15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4210,31 +4206,31 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="Y15" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="Y15" t="s" s="2">
+      <c r="Z15" t="s" s="2">
         <v>180</v>
       </c>
-      <c r="Z15" t="s" s="2">
+      <c r="AA15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE15" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF15" t="s" s="2">
         <v>181</v>
-      </c>
-      <c r="AA15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE15" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF15" t="s" s="2">
-        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4269,14 +4265,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4295,16 +4291,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="L16" t="s" s="2">
         <v>185</v>
       </c>
-      <c r="L16" t="s" s="2">
+      <c r="M16" t="s" s="2">
         <v>186</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="N16" t="s" s="2">
         <v>187</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4354,7 +4350,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4378,7 +4374,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4389,14 +4385,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4415,16 +4411,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>193</v>
       </c>
-      <c r="L17" t="s" s="2">
+      <c r="M17" t="s" s="2">
         <v>194</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>195</v>
-      </c>
-      <c r="N17" t="s" s="2">
-        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4474,7 +4470,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4498,7 +4494,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4509,10 +4505,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4538,10 +4534,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>200</v>
-      </c>
-      <c r="M18" t="s" s="2">
-        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4590,7 +4586,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4625,13 +4621,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C19" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C19" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4653,13 +4649,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="L19" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="M19" t="s" s="2">
         <v>206</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4710,7 +4706,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4719,7 +4715,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -4743,15 +4739,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="B20" t="s" s="2">
+        <v>198</v>
+      </c>
+      <c r="C20" t="s" s="2">
         <v>209</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>210</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>83</v>
@@ -4773,13 +4769,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4830,7 +4826,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4865,10 +4861,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4894,16 +4890,16 @@
         <v>115</v>
       </c>
       <c r="L21" t="s" s="2">
+        <v>214</v>
+      </c>
+      <c r="M21" t="s" s="2">
         <v>215</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4952,7 +4948,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4976,7 +4972,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4987,10 +4983,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5013,17 +5009,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L22" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="M22" t="s" s="2">
         <v>221</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5072,7 +5068,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5087,19 +5083,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="AL22" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AL22" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>227</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -5107,14 +5103,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5133,17 +5129,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
+        <v>229</v>
+      </c>
+      <c r="L23" t="s" s="2">
         <v>230</v>
       </c>
-      <c r="L23" t="s" s="2">
+      <c r="M23" t="s" s="2">
         <v>231</v>
-      </c>
-      <c r="M23" t="s" s="2">
-        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5192,7 +5188,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5207,16 +5203,16 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>233</v>
+      </c>
+      <c r="AL23" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>234</v>
       </c>
-      <c r="AL23" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM23" t="s" s="2">
+      <c r="AN23" t="s" s="2">
         <v>235</v>
-      </c>
-      <c r="AN23" t="s" s="2">
-        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5227,14 +5223,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5253,16 +5249,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="L24" t="s" s="2">
         <v>239</v>
       </c>
-      <c r="L24" t="s" s="2">
+      <c r="M24" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="N24" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5312,7 +5308,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5327,30 +5323,30 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AN24" t="s" s="2">
+      <c r="AO24" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP24" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="25" hidden="true">
+      <c r="A25" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AO24" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>246</v>
-      </c>
       <c r="B25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5373,19 +5369,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>246</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>247</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>248</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>249</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5410,11 +5406,11 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5432,7 +5428,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5447,19 +5443,19 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="AL25" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="AL25" t="s" s="2">
+      <c r="AM25" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="AM25" t="s" s="2">
+      <c r="AN25" t="s" s="2">
         <v>255</v>
       </c>
-      <c r="AN25" t="s" s="2">
+      <c r="AO25" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AO25" t="s" s="2">
-        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5467,10 +5463,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5493,19 +5489,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5530,19 +5526,19 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y26" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z26" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z26" t="s" s="2">
+      <c r="AA26" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB26" t="s" s="2">
         <v>265</v>
-      </c>
-      <c r="AA26" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB26" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5552,7 +5548,7 @@
         <v>121</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5576,24 +5572,24 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AO26" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AO26" t="s" s="2">
+      <c r="AP26" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" hidden="true">
+      <c r="A27" t="s" s="2">
         <v>268</v>
       </c>
-      <c r="AP26" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="s" s="2">
+      <c r="B27" t="s" s="2">
+        <v>257</v>
+      </c>
+      <c r="C27" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="B27" t="s" s="2">
-        <v>258</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>270</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>83</v>
@@ -5615,19 +5611,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="L27" t="s" s="2">
         <v>259</v>
       </c>
-      <c r="L27" t="s" s="2">
+      <c r="M27" t="s" s="2">
         <v>260</v>
       </c>
-      <c r="M27" t="s" s="2">
+      <c r="N27" t="s" s="2">
         <v>261</v>
       </c>
-      <c r="N27" t="s" s="2">
+      <c r="O27" t="s" s="2">
         <v>262</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>263</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5652,14 +5648,14 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y27" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="Z27" t="s" s="2">
         <v>264</v>
       </c>
-      <c r="Z27" t="s" s="2">
-        <v>265</v>
-      </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
       </c>
@@ -5676,7 +5672,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5700,10 +5696,10 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
+        <v>266</v>
+      </c>
+      <c r="AO27" t="s" s="2">
         <v>267</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>268</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5711,10 +5707,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="B28" t="s" s="2">
         <v>271</v>
-      </c>
-      <c r="B28" t="s" s="2">
-        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5829,10 +5825,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="B29" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="B29" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5947,12 +5943,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="B30" t="s" s="2">
         <v>275</v>
-      </c>
-      <c r="B30" t="s" s="2">
-        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5975,19 +5971,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M30" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="N30" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -6036,7 +6032,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6057,10 +6053,10 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN30" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -6071,10 +6067,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="B31" t="s" s="2">
         <v>284</v>
-      </c>
-      <c r="B31" t="s" s="2">
-        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6189,10 +6185,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="B32" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="B32" t="s" s="2">
-        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6307,12 +6303,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="B33" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6338,65 +6334,65 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M33" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M33" t="s" s="2">
+      <c r="N33" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N33" t="s" s="2">
+      <c r="O33" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O33" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="S33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6417,10 +6413,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AN33" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6431,10 +6427,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="B34" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="B34" t="s" s="2">
-        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6460,13 +6456,13 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6516,7 +6512,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6537,24 +6533,24 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN34" t="s" s="2">
         <v>304</v>
       </c>
-      <c r="AN34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP34" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
         <v>305</v>
       </c>
-      <c r="AO34" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP34" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
+      <c r="B35" t="s" s="2">
         <v>306</v>
-      </c>
-      <c r="B35" t="s" s="2">
-        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6577,66 +6573,66 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L35" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M35" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M35" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="S35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6657,10 +6653,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6671,10 +6667,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="B36" t="s" s="2">
         <v>315</v>
-      </c>
-      <c r="B36" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6700,14 +6696,14 @@
         <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6756,7 +6752,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6777,10 +6773,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6791,10 +6787,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="B37" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="B37" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6817,19 +6813,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="N37" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6878,7 +6874,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6899,10 +6895,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6913,10 +6909,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B38" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B38" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6942,16 +6938,16 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M38" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M38" t="s" s="2">
+      <c r="N38" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N38" t="s" s="2">
+      <c r="O38" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O38" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -7000,7 +6996,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7021,28 +7017,28 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN38" t="s" s="2">
+      <c r="AO38" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP38" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" hidden="true">
+      <c r="A39" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AO38" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP38" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="s" s="2">
-        <v>342</v>
-      </c>
       <c r="B39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7061,19 +7057,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>344</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>345</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>346</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>347</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7098,14 +7094,14 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y39" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z39" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z39" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
       </c>
@@ -7122,7 +7118,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>94</v>
@@ -7137,30 +7133,30 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>350</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AM39" t="s" s="2">
         <v>351</v>
       </c>
-      <c r="AM39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>352</v>
       </c>
-      <c r="AN39" t="s" s="2">
+      <c r="AO39" t="s" s="2">
         <v>353</v>
       </c>
-      <c r="AO39" t="s" s="2">
+      <c r="AP39" t="s" s="2">
         <v>354</v>
-      </c>
-      <c r="AP39" t="s" s="2">
-        <v>355</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7275,10 +7271,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7395,10 +7391,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7421,19 +7417,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M42" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M42" t="s" s="2">
+      <c r="N42" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N42" t="s" s="2">
+      <c r="O42" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7470,7 +7466,7 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7480,7 +7476,7 @@
         <v>121</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7501,10 +7497,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN42" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7515,13 +7511,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="B43" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="C43" t="s" s="2">
         <v>360</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="C43" t="s" s="2">
-        <v>361</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -7543,19 +7539,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="L43" t="s" s="2">
+        <v>276</v>
+      </c>
+      <c r="M43" t="s" s="2">
         <v>277</v>
       </c>
-      <c r="M43" t="s" s="2">
+      <c r="N43" t="s" s="2">
         <v>278</v>
       </c>
-      <c r="N43" t="s" s="2">
+      <c r="O43" t="s" s="2">
         <v>279</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>280</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7604,7 +7600,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7625,10 +7621,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AN43" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7639,10 +7635,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="B44" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7757,10 +7753,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="B45" t="s" s="2">
         <v>364</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7877,10 +7873,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="B46" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7906,23 +7902,23 @@
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>289</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>290</v>
       </c>
-      <c r="M46" t="s" s="2">
+      <c r="N46" t="s" s="2">
         <v>291</v>
       </c>
-      <c r="N46" t="s" s="2">
+      <c r="O46" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="O46" t="s" s="2">
-        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7964,7 +7960,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7985,10 +7981,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AN46" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7999,10 +7995,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="B47" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8028,13 +8024,13 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>300</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>301</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>302</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8084,7 +8080,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8105,10 +8101,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AN47" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8119,10 +8115,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="B48" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="B48" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8145,24 +8141,24 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L48" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="M48" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="M48" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8204,7 +8200,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8225,10 +8221,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>313</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>314</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8239,10 +8235,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="B49" t="s" s="2">
         <v>374</v>
-      </c>
-      <c r="B49" t="s" s="2">
-        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8268,14 +8264,14 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="M49" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="M49" t="s" s="2">
-        <v>318</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8324,7 +8320,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8345,10 +8341,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>321</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>322</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8359,10 +8355,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>376</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8385,19 +8381,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="L50" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="L50" t="s" s="2">
+      <c r="M50" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="N50" t="s" s="2">
         <v>327</v>
       </c>
-      <c r="N50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>329</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8446,7 +8442,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8467,10 +8463,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AN50" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8481,10 +8477,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8510,16 +8506,16 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="M51" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="M51" t="s" s="2">
+      <c r="N51" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="N51" t="s" s="2">
+      <c r="O51" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8568,7 +8564,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8589,11 +8585,11 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="AN51" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AN51" t="s" s="2">
-        <v>341</v>
-      </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
       </c>
@@ -8601,12 +8597,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8629,19 +8625,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="L52" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="L52" t="s" s="2">
+      <c r="M52" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="N52" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="N52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>383</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8690,7 +8686,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8705,19 +8701,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>385</v>
       </c>
-      <c r="AL52" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>386</v>
       </c>
-      <c r="AN52" t="s" s="2">
+      <c r="AO52" t="s" s="2">
         <v>387</v>
-      </c>
-      <c r="AO52" t="s" s="2">
-        <v>388</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8725,10 +8721,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8751,16 +8747,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="L53" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="L53" t="s" s="2">
+      <c r="M53" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="M53" t="s" s="2">
+      <c r="N53" t="s" s="2">
         <v>392</v>
-      </c>
-      <c r="N53" t="s" s="2">
-        <v>393</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8810,7 +8806,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8831,13 +8827,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8845,14 +8841,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8871,19 +8867,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="L54" t="s" s="2">
         <v>397</v>
       </c>
-      <c r="L54" t="s" s="2">
+      <c r="M54" t="s" s="2">
         <v>398</v>
       </c>
-      <c r="M54" t="s" s="2">
+      <c r="N54" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="N54" t="s" s="2">
+      <c r="O54" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="O54" t="s" s="2">
-        <v>401</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8932,7 +8928,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8947,34 +8943,34 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="AN54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>404</v>
       </c>
-      <c r="AO54" t="s" s="2">
+      <c r="AP54" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="55" hidden="true">
+      <c r="A55" t="s" s="2">
         <v>405</v>
       </c>
-      <c r="AP54" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>406</v>
-      </c>
       <c r="B55" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8993,19 +8989,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="L55" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="L55" t="s" s="2">
+      <c r="M55" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="M55" t="s" s="2">
+      <c r="N55" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="N55" t="s" s="2">
+      <c r="O55" t="s" s="2">
         <v>411</v>
-      </c>
-      <c r="O55" t="s" s="2">
-        <v>412</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9054,7 +9050,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9063,25 +9059,25 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="AJ55" t="s" s="2">
         <v>413</v>
       </c>
-      <c r="AJ55" t="s" s="2">
+      <c r="AK55" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="AK55" t="s" s="2">
+      <c r="AL55" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="AL55" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>416</v>
       </c>
-      <c r="AN55" t="s" s="2">
+      <c r="AO55" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AO55" t="s" s="2">
-        <v>418</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9089,10 +9085,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9118,13 +9114,13 @@
         <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M56" t="s" s="2">
         <v>420</v>
       </c>
-      <c r="M56" t="s" s="2">
+      <c r="N56" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>422</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9174,7 +9170,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9195,13 +9191,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="AN56" t="s" s="2">
         <v>423</v>
       </c>
-      <c r="AN56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>424</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>425</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9209,10 +9205,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9235,17 +9231,17 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="L57" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="L57" t="s" s="2">
+      <c r="M57" t="s" s="2">
         <v>428</v>
-      </c>
-      <c r="M57" t="s" s="2">
-        <v>429</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9294,7 +9290,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9309,19 +9305,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>431</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>432</v>
       </c>
-      <c r="AN57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>433</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>434</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9329,10 +9325,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9355,19 +9351,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L58" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L58" t="s" s="2">
+      <c r="M58" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M58" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N58" t="s" s="2">
+      <c r="O58" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9404,17 +9400,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9423,7 +9419,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9432,30 +9428,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP58" t="s" s="2">
         <v>445</v>
       </c>
-      <c r="AO58" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP58" t="s" s="2">
+    </row>
+    <row r="59" hidden="true">
+      <c r="A59" t="s" s="2">
         <v>446</v>
       </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="s" s="2">
+      <c r="B59" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="C59" t="s" s="2">
         <v>447</v>
-      </c>
-      <c r="B59" t="s" s="2">
-        <v>435</v>
-      </c>
-      <c r="C59" t="s" s="2">
-        <v>448</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9477,19 +9473,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>435</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>436</v>
       </c>
-      <c r="L59" t="s" s="2">
+      <c r="M59" t="s" s="2">
+        <v>436</v>
+      </c>
+      <c r="N59" t="s" s="2">
         <v>437</v>
       </c>
-      <c r="M59" t="s" s="2">
-        <v>437</v>
-      </c>
-      <c r="N59" t="s" s="2">
+      <c r="O59" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="O59" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9538,7 +9534,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9547,7 +9543,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9556,27 +9552,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>443</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="AN59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP59" t="s" s="2">
         <v>445</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP59" t="s" s="2">
-        <v>446</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="B60" t="s" s="2">
         <v>449</v>
-      </c>
-      <c r="B60" t="s" s="2">
-        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9691,10 +9687,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B61" t="s" s="2">
         <v>451</v>
-      </c>
-      <c r="B61" t="s" s="2">
-        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9809,12 +9805,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="B62" t="s" s="2">
         <v>453</v>
-      </c>
-      <c r="B62" t="s" s="2">
-        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9837,19 +9833,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L62" t="s" s="2">
         <v>455</v>
       </c>
-      <c r="L62" t="s" s="2">
+      <c r="M62" t="s" s="2">
         <v>456</v>
       </c>
-      <c r="M62" t="s" s="2">
+      <c r="N62" t="s" s="2">
         <v>457</v>
       </c>
-      <c r="N62" t="s" s="2">
+      <c r="O62" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="O62" t="s" s="2">
-        <v>459</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9898,7 +9894,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9919,10 +9915,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9933,10 +9929,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="B63" t="s" s="2">
         <v>463</v>
-      </c>
-      <c r="B63" t="s" s="2">
-        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9959,68 +9955,68 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>464</v>
+      </c>
+      <c r="M63" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="M63" t="s" s="2">
-        <v>466</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="P63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Q63" t="s" s="2">
         <v>467</v>
       </c>
-      <c r="P63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Q63" t="s" s="2">
+      <c r="R63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="S63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X63" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="Y63" t="s" s="2">
         <v>468</v>
       </c>
-      <c r="R63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="S63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X63" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="Y63" t="s" s="2">
+      <c r="Z63" t="s" s="2">
         <v>469</v>
       </c>
-      <c r="Z63" t="s" s="2">
+      <c r="AA63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>470</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10041,24 +10037,24 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AN63" t="s" s="2">
         <v>472</v>
       </c>
-      <c r="AN63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
         <v>473</v>
       </c>
-      <c r="AO63" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP63" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="2">
+      <c r="B64" t="s" s="2">
         <v>474</v>
-      </c>
-      <c r="B64" t="s" s="2">
-        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10084,14 +10080,14 @@
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="M64" t="s" s="2">
         <v>476</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>477</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10140,7 +10136,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10161,24 +10157,24 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="AN64" t="s" s="2">
         <v>480</v>
       </c>
-      <c r="AN64" t="s" s="2">
+      <c r="AO64" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
         <v>481</v>
       </c>
-      <c r="AO64" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP64" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="s" s="2">
+      <c r="B65" t="s" s="2">
         <v>482</v>
-      </c>
-      <c r="B65" t="s" s="2">
-        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10204,63 +10200,63 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="M65" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="M65" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF65" t="s" s="2">
         <v>487</v>
-      </c>
-      <c r="S65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="T65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="U65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="V65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="W65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="X65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Y65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="Z65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AA65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF65" t="s" s="2">
-        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10269,7 +10265,7 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
@@ -10281,24 +10277,24 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AN65" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="AO65" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP65" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="s" s="2">
+      <c r="B66" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="B66" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10321,19 +10317,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L66" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N66" t="s" s="2">
         <v>493</v>
       </c>
-      <c r="M66" t="s" s="2">
-        <v>493</v>
-      </c>
-      <c r="N66" t="s" s="2">
+      <c r="O66" t="s" s="2">
         <v>494</v>
-      </c>
-      <c r="O66" t="s" s="2">
-        <v>495</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10358,31 +10354,31 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="Z66" t="s" s="2">
         <v>496</v>
       </c>
-      <c r="Z66" t="s" s="2">
+      <c r="AA66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10403,24 +10399,24 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="AN66" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
         <v>499</v>
       </c>
-      <c r="AO66" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP66" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="s" s="2">
-        <v>500</v>
-      </c>
       <c r="B67" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10443,19 +10439,19 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L67" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M67" t="s" s="2">
         <v>501</v>
       </c>
-      <c r="M67" t="s" s="2">
+      <c r="N67" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N67" t="s" s="2">
+      <c r="O67" t="s" s="2">
         <v>503</v>
-      </c>
-      <c r="O67" t="s" s="2">
-        <v>504</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10480,14 +10476,14 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y67" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z67" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z67" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
       </c>
@@ -10504,7 +10500,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10513,7 +10509,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10525,10 +10521,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10539,14 +10535,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10565,19 +10561,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M68" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M68" t="s" s="2">
+      <c r="N68" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N68" t="s" s="2">
+      <c r="O68" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O68" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10602,14 +10598,14 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y68" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z68" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Z68" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
       </c>
@@ -10626,7 +10622,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10644,27 +10640,27 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AM68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AN68" t="s" s="2">
+      <c r="AO68" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP68" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AO68" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP68" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10687,19 +10683,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="L69" t="s" s="2">
         <v>522</v>
       </c>
-      <c r="L69" t="s" s="2">
+      <c r="M69" t="s" s="2">
         <v>523</v>
       </c>
-      <c r="M69" t="s" s="2">
+      <c r="N69" t="s" s="2">
         <v>524</v>
       </c>
-      <c r="N69" t="s" s="2">
+      <c r="O69" t="s" s="2">
         <v>525</v>
-      </c>
-      <c r="O69" t="s" s="2">
-        <v>526</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10748,7 +10744,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10769,10 +10765,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="AN69" t="s" s="2">
         <v>527</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>528</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10783,10 +10779,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10809,16 +10805,16 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L70" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M70" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M70" t="s" s="2">
+      <c r="N70" t="s" s="2">
         <v>531</v>
-      </c>
-      <c r="N70" t="s" s="2">
-        <v>532</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10844,14 +10840,14 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="Z70" t="s" s="2">
         <v>533</v>
       </c>
-      <c r="Z70" t="s" s="2">
-        <v>534</v>
-      </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
       </c>
@@ -10868,7 +10864,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10886,27 +10882,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>535</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>536</v>
       </c>
-      <c r="AN70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP70" t="s" s="2">
         <v>537</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP70" t="s" s="2">
-        <v>538</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10929,19 +10925,19 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M71" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="M71" t="s" s="2">
+      <c r="N71" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="N71" t="s" s="2">
+      <c r="O71" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="O71" t="s" s="2">
-        <v>543</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10966,11 +10962,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10988,7 +10984,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11009,10 +11005,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AN71" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="AN71" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11023,10 +11019,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11049,16 +11045,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>548</v>
       </c>
-      <c r="L72" t="s" s="2">
+      <c r="M72" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="M72" t="s" s="2">
+      <c r="N72" t="s" s="2">
         <v>550</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>551</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11108,7 +11104,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11126,27 +11122,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>553</v>
       </c>
-      <c r="AN72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP72" t="s" s="2">
         <v>554</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP72" t="s" s="2">
-        <v>555</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11169,16 +11165,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="L73" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="L73" t="s" s="2">
+      <c r="M73" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="M73" t="s" s="2">
+      <c r="N73" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>560</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11228,7 +11224,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11246,27 +11242,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>561</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AN73" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AN73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP73" t="s" s="2">
         <v>563</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP73" t="s" s="2">
-        <v>564</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11289,19 +11285,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="L74" t="s" s="2">
         <v>566</v>
       </c>
-      <c r="L74" t="s" s="2">
+      <c r="M74" t="s" s="2">
         <v>567</v>
       </c>
-      <c r="M74" t="s" s="2">
+      <c r="N74" t="s" s="2">
         <v>568</v>
       </c>
-      <c r="N74" t="s" s="2">
+      <c r="O74" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11350,7 +11346,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11362,19 +11358,19 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM74" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="AK74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM74" t="s" s="2">
+      <c r="AN74" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11385,10 +11381,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11503,10 +11499,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11623,14 +11619,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11652,16 +11648,16 @@
         <v>115</v>
       </c>
       <c r="L77" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M77" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M77" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11710,7 +11706,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11734,7 +11730,7 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11745,10 +11741,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11771,13 +11767,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="L78" t="s" s="2">
         <v>582</v>
       </c>
-      <c r="L78" t="s" s="2">
+      <c r="M78" t="s" s="2">
         <v>583</v>
-      </c>
-      <c r="M78" t="s" s="2">
-        <v>584</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11828,7 +11824,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11837,7 +11833,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11849,10 +11845,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>586</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>587</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11863,10 +11859,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11889,13 +11885,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="L79" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="M79" t="s" s="2">
         <v>589</v>
-      </c>
-      <c r="M79" t="s" s="2">
-        <v>590</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11946,7 +11942,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11955,7 +11951,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11967,10 +11963,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11981,10 +11977,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12007,19 +12003,19 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L80" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="M80" t="s" s="2">
         <v>593</v>
       </c>
-      <c r="M80" t="s" s="2">
+      <c r="N80" t="s" s="2">
         <v>594</v>
       </c>
-      <c r="N80" t="s" s="2">
+      <c r="O80" t="s" s="2">
         <v>595</v>
-      </c>
-      <c r="O80" t="s" s="2">
-        <v>596</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12044,14 +12040,14 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="Y80" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="Z80" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="Z80" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
       </c>
@@ -12068,7 +12064,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12086,13 +12082,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AM80" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AM80" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="AN80" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12103,10 +12099,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12129,19 +12125,19 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L81" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="M81" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="M81" t="s" s="2">
+      <c r="N81" t="s" s="2">
         <v>603</v>
       </c>
-      <c r="N81" t="s" s="2">
+      <c r="O81" t="s" s="2">
         <v>604</v>
-      </c>
-      <c r="O81" t="s" s="2">
-        <v>605</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12166,14 +12162,14 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="Y81" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="Z81" t="s" s="2">
         <v>606</v>
       </c>
-      <c r="Z81" t="s" s="2">
-        <v>607</v>
-      </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
       </c>
@@ -12190,7 +12186,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12208,13 +12204,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="AM81" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="AM81" t="s" s="2">
-        <v>600</v>
-      </c>
       <c r="AN81" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12225,10 +12221,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12251,17 +12247,17 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="L82" t="s" s="2">
         <v>609</v>
       </c>
-      <c r="L82" t="s" s="2">
+      <c r="M82" t="s" s="2">
         <v>610</v>
-      </c>
-      <c r="M82" t="s" s="2">
-        <v>611</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12310,7 +12306,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12334,7 +12330,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12345,10 +12341,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12374,10 +12370,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="M83" t="s" s="2">
         <v>615</v>
-      </c>
-      <c r="M83" t="s" s="2">
-        <v>616</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12428,7 +12424,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12449,10 +12445,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12463,10 +12459,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12489,16 +12485,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="L84" t="s" s="2">
         <v>619</v>
       </c>
-      <c r="L84" t="s" s="2">
+      <c r="M84" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="M84" t="s" s="2">
+      <c r="N84" t="s" s="2">
         <v>621</v>
-      </c>
-      <c r="N84" t="s" s="2">
-        <v>622</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12548,7 +12544,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12569,10 +12565,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AN84" t="s" s="2">
         <v>623</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>624</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12583,10 +12579,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12609,16 +12605,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="L85" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="L85" t="s" s="2">
+      <c r="M85" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="M85" t="s" s="2">
+      <c r="N85" t="s" s="2">
         <v>628</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>629</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12668,7 +12664,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12689,24 +12685,24 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="AN85" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
         <v>630</v>
       </c>
-      <c r="AO85" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP85" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>631</v>
-      </c>
       <c r="B86" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12729,19 +12725,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="L86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N86" t="s" s="2">
         <v>632</v>
       </c>
-      <c r="M86" t="s" s="2">
-        <v>632</v>
-      </c>
-      <c r="N86" t="s" s="2">
+      <c r="O86" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12790,7 +12786,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12802,19 +12798,19 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
+        <v>634</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>635</v>
       </c>
-      <c r="AK86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AL86" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AM86" t="s" s="2">
+      <c r="AN86" t="s" s="2">
         <v>636</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>637</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12825,10 +12821,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12943,10 +12939,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13063,14 +13059,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13092,16 +13088,16 @@
         <v>115</v>
       </c>
       <c r="L89" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M89" t="s" s="2">
         <v>578</v>
-      </c>
-      <c r="M89" t="s" s="2">
-        <v>579</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13150,7 +13146,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13174,7 +13170,7 @@
         <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13183,12 +13179,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13211,19 +13207,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L90" t="s" s="2">
+        <v>641</v>
+      </c>
+      <c r="M90" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="M90" t="s" s="2">
+      <c r="N90" t="s" s="2">
         <v>643</v>
       </c>
-      <c r="N90" t="s" s="2">
+      <c r="O90" t="s" s="2">
         <v>644</v>
-      </c>
-      <c r="O90" t="s" s="2">
-        <v>645</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13248,14 +13244,14 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y90" t="s" s="2">
+        <v>347</v>
+      </c>
+      <c r="Z90" t="s" s="2">
         <v>348</v>
       </c>
-      <c r="Z90" t="s" s="2">
-        <v>349</v>
-      </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
       </c>
@@ -13272,7 +13268,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13290,27 +13286,27 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>645</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>352</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>353</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
         <v>646</v>
       </c>
-      <c r="AM90" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AO90" t="s" s="2">
-        <v>354</v>
-      </c>
-      <c r="AP90" t="s" s="2">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="2">
-        <v>647</v>
-      </c>
       <c r="B91" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13333,19 +13329,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>647</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>648</v>
       </c>
-      <c r="L91" t="s" s="2">
+      <c r="M91" t="s" s="2">
         <v>649</v>
       </c>
-      <c r="M91" t="s" s="2">
+      <c r="N91" t="s" s="2">
         <v>650</v>
       </c>
-      <c r="N91" t="s" s="2">
-        <v>651</v>
-      </c>
       <c r="O91" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13370,14 +13366,14 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y91" t="s" s="2">
+        <v>651</v>
+      </c>
+      <c r="Z91" t="s" s="2">
         <v>652</v>
       </c>
-      <c r="Z91" t="s" s="2">
-        <v>653</v>
-      </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
       </c>
@@ -13394,7 +13390,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13403,7 +13399,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13412,27 +13408,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>654</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
         <v>655</v>
       </c>
-      <c r="AM91" t="s" s="2">
-        <v>444</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>445</v>
-      </c>
-      <c r="AO91" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP91" t="s" s="2">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s" s="2">
-        <v>656</v>
-      </c>
       <c r="B92" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13455,19 +13451,19 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L92" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M92" t="s" s="2">
         <v>657</v>
       </c>
-      <c r="M92" t="s" s="2">
+      <c r="N92" t="s" s="2">
         <v>658</v>
       </c>
-      <c r="N92" t="s" s="2">
-        <v>659</v>
-      </c>
       <c r="O92" t="s" s="2">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13492,14 +13488,14 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y92" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="Z92" t="s" s="2">
         <v>505</v>
       </c>
-      <c r="Z92" t="s" s="2">
-        <v>506</v>
-      </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
       </c>
@@ -13516,7 +13512,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13525,7 +13521,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13537,10 +13533,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13551,14 +13547,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13577,19 +13573,19 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L93" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="M93" t="s" s="2">
         <v>511</v>
       </c>
-      <c r="M93" t="s" s="2">
+      <c r="N93" t="s" s="2">
         <v>512</v>
       </c>
-      <c r="N93" t="s" s="2">
+      <c r="O93" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13614,14 +13610,14 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="Y93" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="Z93" t="s" s="2">
         <v>515</v>
       </c>
-      <c r="Z93" t="s" s="2">
-        <v>516</v>
-      </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
       </c>
@@ -13638,7 +13634,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13656,27 +13652,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>517</v>
       </c>
-      <c r="AM93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>518</v>
       </c>
-      <c r="AN93" t="s" s="2">
+      <c r="AO93" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AP93" t="s" s="2">
         <v>519</v>
-      </c>
-      <c r="AO93" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AP93" t="s" s="2">
-        <v>520</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13702,16 +13698,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
+        <v>662</v>
+      </c>
+      <c r="M94" t="s" s="2">
         <v>663</v>
       </c>
-      <c r="M94" t="s" s="2">
-        <v>664</v>
-      </c>
       <c r="N94" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="O94" t="s" s="2">
         <v>569</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>570</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13760,7 +13756,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13781,10 +13777,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="AN94" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13795,12 +13791,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP94">
-    <filterColumn colId="7">
+    <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="27">
+    <filterColumn colId="26">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-height.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-observation-body-height.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="664">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3637" uniqueCount="665">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,10 +72,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile for body height.
+    <t>French profile for body height.
 Profil français de la mesure de la taille. Profil basé sur le profil bodyheight d'HL7</t>
   </si>
   <si>
@@ -118,7 +118,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/bodyheight</t>
+    <t>http://hl7.org/fhir/StructureDefinition/bodyheight|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -446,7 +446,7 @@
     <t>Identifies where the resource comes from</t>
   </si>
   <si>
-    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
+    <t>A uri that identifies the source system of the resource. This provides a minimal amount of [Provenance](http://hl7.org/fhir/R4/provenance.html#) information that can be used to track or differentiate the source of information in the resource. The source may identify another FHIR server, document, message, database, etc.</t>
   </si>
   <si>
     <t>In the provenance resource, this corresponds to Provenance.entity.what[x]. The exact use of the source (and the implied Provenance.entity.role) is left to implementer discretion. Only one nominated source is allowed; for additional provenance details, a full Provenance resource should be used. 
@@ -459,14 +459,14 @@
     <t>Observation.meta.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
     <t>Profiles this resource claims to conform to</t>
   </si>
   <si>
-    <t>A list of profiles (references to [StructureDefinition](structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](structuredefinition-definitions.html#StructureDefinition.url).</t>
+    <t>A list of profiles (references to [StructureDefinition](http://hl7.org/fhir/R4/structuredefinition.html#) resources) that this resource claims to conform to. The URL is a reference to [StructureDefinition.url](http://hl7.org/fhir/R4/structuredefinition-definitions.html#StructureDefinition.url).</t>
   </si>
   <si>
     <t>It is up to the server and/or other infrastructure of policy to determine whether/how these claims are verified and/or updated over time.  The list of profile URLs is a set.</t>
@@ -488,6 +488,9 @@
     <t>fr-canonical</t>
   </si>
   <si>
+    <t>https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-body-height|2.2.0</t>
+  </si>
+  <si>
     <t>Observation.meta.security</t>
   </si>
   <si>
@@ -510,7 +513,7 @@
     <t>Security Labels from the Healthcare Privacy and Security Classification System.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/security-labels</t>
+    <t>http://hl7.org/fhir/ValueSet/security-labels|4.0.1</t>
   </si>
   <si>
     <t>Meta.security</t>
@@ -534,7 +537,7 @@
     <t>Codes that represent various types of tags, commonly workflow-related; e.g. "Needs review by Dr. Jones".</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/common-tags</t>
+    <t>http://hl7.org/fhir/ValueSet/common-tags|4.0.1</t>
   </si>
   <si>
     <t>Meta.tag</t>
@@ -577,7 +580,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -653,14 +656,15 @@
     <t>bodyposition</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position}
+    <t xml:space="preserve">Extension {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-observation-height-body-position|2.2.0}
 </t>
   </si>
   <si>
     <t>FR Core Observation Height Body Position Extension</t>
   </si>
   <si>
-    <t>Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height. | Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing)</t>
+    <t>Extension utilisée par le profil FrObservationBodyHeight permettant de préciser la position du corps durant la mesure de la taille (le jeu de valeur associé est limité aux 2 valeurs lying et standing).
+Extension on the FrObservationBodyHeight to specify the position of the body during the measure of the height.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -673,7 +677,7 @@
     <t>supportingInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {workflow-supportingInfo}
+    <t xml:space="preserve">Extension {workflow-supportingInfo|5.2.0}
 </t>
   </si>
   <si>
@@ -734,7 +738,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CarePlan|DeviceRequest|ImmunizationRecommendation|MedicationRequest|NutritionOrder|ServiceRequest)
+    <t xml:space="preserve">Reference(CarePlan|4.0.1|DeviceRequest|4.0.1|ImmunizationRecommendation|4.0.1|MedicationRequest|4.0.1|NutritionOrder|4.0.1|ServiceRequest|4.0.1)
 </t>
   </si>
   <si>
@@ -763,7 +767,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(MedicationAdministration|MedicationDispense|MedicationStatement|Procedure|Immunization|ImagingStudy)
+    <t xml:space="preserve">Reference(MedicationAdministration|4.0.1|MedicationDispense|4.0.1|MedicationStatement|4.0.1|Procedure|4.0.1|Immunization|4.0.1|ImagingStudy|4.0.1)
 </t>
   </si>
   <si>
@@ -843,7 +847,7 @@
     <t>Codes for high level observation categories.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-category</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-category|4.0.1</t>
   </si>
   <si>
     <t>value:coding.code}
@@ -1098,7 +1102,7 @@
     <t>This identifies the vital sign result type.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-vitalsignresult|4.0.1</t>
   </si>
   <si>
     <t>Event.code</t>
@@ -1192,7 +1196,7 @@
     <t>Observation.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0)
 </t>
   </si>
   <si>
@@ -1223,7 +1227,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -1246,7 +1250,7 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-encounter|2.2.0)
 </t>
   </si>
   <si>
@@ -1341,7 +1345,7 @@
     <t>Observation.performer</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(CareTeam|RelatedPerson|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|PractitionerRole|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization)
+    <t xml:space="preserve">Reference(CareTeam|4.0.1|RelatedPerson|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-patient|2.2.0|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-practitioner|2.2.0|PractitionerRole|4.0.1|https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0)
 </t>
   </si>
   <si>
@@ -1585,7 +1589,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t>obs-6
@@ -1617,7 +1621,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1673,7 +1677,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1703,7 +1707,7 @@
     <t>In some cases, method can impact results and is thus used for determining whether results can be compared or determining significance of results.</t>
   </si>
   <si>
-    <t>http://models.opencimi.org/ig/vital-signs-fhir-profiles/ValueSet-heightLengthMeasMethodVS</t>
+    <t>https://hl7.fr/ig/fhir/core/ValueSet/fr-core-vs-height-meas-method|2.2.0</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1715,7 +1719,7 @@
     <t>Observation.specimen</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Specimen)
+    <t xml:space="preserve">Reference(Specimen|4.0.1)
 </t>
   </si>
   <si>
@@ -1743,7 +1747,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1823,7 +1827,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1873,7 +1877,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1906,7 +1910,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1943,7 +1947,7 @@
     <t>Observation.hasMember</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -1965,7 +1969,7 @@
     <t>Observation.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DocumentReference|ImagingStudy|Media|QuestionnaireResponse|MolecularSequence|vitalsigns)
+    <t xml:space="preserve">Reference(DocumentReference|4.0.1|ImagingStudy|4.0.1|Media|4.0.1|QuestionnaireResponse|4.0.1|MolecularSequence|4.0.1|vitalsigns|4.0.1)
 </t>
   </si>
   <si>
@@ -2414,17 +2418,17 @@
   <dimension ref="A1:AP94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="50.29296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="42.9296875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="15.76953125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.4609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.3828125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="37.03125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.60546875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="33.17578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="226.43359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="222.875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2433,28 +2437,28 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.2265625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="85.80859375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="39.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="82.14453125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="59.453125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="34.0078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="26.69140625" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="245.78125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="23.0234375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="212.015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="102.73828125" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="33.05078125" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="38.60546875" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="88.625" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="28.5078125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="33.30078125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3711,7 +3715,7 @@
         <v>83</v>
       </c>
       <c r="S11" t="s" s="2">
-        <v>3</v>
+        <v>151</v>
       </c>
       <c r="T11" t="s" s="2">
         <v>83</v>
@@ -3785,10 +3789,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3811,16 +3815,16 @@
         <v>95</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3846,13 +3850,13 @@
         <v>83</v>
       </c>
       <c r="X12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>83</v>
@@ -3870,7 +3874,7 @@
         <v>83</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>81</v>
@@ -3905,10 +3909,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3931,16 +3935,16 @@
         <v>95</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3966,13 +3970,13 @@
         <v>83</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="Z13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>83</v>
@@ -3990,7 +3994,7 @@
         <v>83</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>81</v>
@@ -4025,10 +4029,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -4054,13 +4058,13 @@
         <v>136</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -4110,7 +4114,7 @@
         <v>83</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -4145,10 +4149,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4171,16 +4175,16 @@
         <v>83</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -4206,13 +4210,13 @@
         <v>83</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>83</v>
@@ -4230,7 +4234,7 @@
         <v>83</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -4265,14 +4269,14 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -4291,16 +4295,16 @@
         <v>83</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
@@ -4350,7 +4354,7 @@
         <v>83</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -4374,7 +4378,7 @@
         <v>83</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AO16" t="s" s="2">
         <v>83</v>
@@ -4385,14 +4389,14 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4411,16 +4415,16 @@
         <v>83</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4470,7 +4474,7 @@
         <v>83</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4494,7 +4498,7 @@
         <v>83</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO17" t="s" s="2">
         <v>83</v>
@@ -4505,10 +4509,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4534,10 +4538,10 @@
         <v>115</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -4586,7 +4590,7 @@
         <v>121</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4621,13 +4625,13 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D19" t="s" s="2">
         <v>83</v>
@@ -4649,13 +4653,13 @@
         <v>83</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4706,7 +4710,7 @@
         <v>83</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4715,7 +4719,7 @@
         <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -4739,15 +4743,15 @@
         <v>83</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>83</v>
@@ -4769,13 +4773,13 @@
         <v>83</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4826,7 +4830,7 @@
         <v>83</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4861,10 +4865,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4890,16 +4894,16 @@
         <v>115</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>83</v>
@@ -4948,7 +4952,7 @@
         <v>83</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4972,7 +4976,7 @@
         <v>83</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO21" t="s" s="2">
         <v>83</v>
@@ -4983,10 +4987,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5009,17 +5013,17 @@
         <v>95</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>83</v>
@@ -5068,7 +5072,7 @@
         <v>83</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>81</v>
@@ -5083,19 +5087,19 @@
         <v>106</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>83</v>
@@ -5103,14 +5107,14 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -5129,17 +5133,17 @@
         <v>95</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>83</v>
@@ -5188,7 +5192,7 @@
         <v>83</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -5203,16 +5207,16 @@
         <v>106</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>83</v>
@@ -5223,14 +5227,14 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
@@ -5249,16 +5253,16 @@
         <v>95</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -5308,7 +5312,7 @@
         <v>83</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -5323,16 +5327,16 @@
         <v>106</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>83</v>
@@ -5341,12 +5345,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="25" hidden="true">
+    <row r="25">
       <c r="A25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5369,19 +5373,19 @@
         <v>95</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>83</v>
@@ -5406,11 +5410,11 @@
         <v>83</v>
       </c>
       <c r="X25" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y25" s="2"/>
       <c r="Z25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>83</v>
@@ -5428,7 +5432,7 @@
         <v>83</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>94</v>
@@ -5443,19 +5447,19 @@
         <v>106</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AP25" t="s" s="2">
         <v>83</v>
@@ -5463,10 +5467,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5489,19 +5493,19 @@
         <v>83</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>83</v>
@@ -5526,19 +5530,19 @@
         <v>83</v>
       </c>
       <c r="X26" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="AC26" s="2"/>
       <c r="AD26" t="s" s="2">
@@ -5548,7 +5552,7 @@
         <v>121</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5572,24 +5576,24 @@
         <v>83</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D27" t="s" s="2">
         <v>83</v>
@@ -5611,19 +5615,19 @@
         <v>83</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>83</v>
@@ -5648,13 +5652,13 @@
         <v>83</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>83</v>
@@ -5672,7 +5676,7 @@
         <v>83</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5696,10 +5700,10 @@
         <v>83</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>83</v>
@@ -5707,10 +5711,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5825,10 +5829,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5943,12 +5947,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5971,19 +5975,19 @@
         <v>95</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>83</v>
@@ -6032,7 +6036,7 @@
         <v>83</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -6053,10 +6057,10 @@
         <v>83</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO30" t="s" s="2">
         <v>83</v>
@@ -6067,10 +6071,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -6185,10 +6189,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6303,12 +6307,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6334,23 +6338,23 @@
         <v>136</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>83</v>
@@ -6392,7 +6396,7 @@
         <v>83</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -6413,10 +6417,10 @@
         <v>83</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>83</v>
@@ -6427,10 +6431,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6456,13 +6460,13 @@
         <v>108</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6512,7 +6516,7 @@
         <v>83</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6533,10 +6537,10 @@
         <v>83</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>83</v>
@@ -6545,12 +6549,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="35" hidden="true">
+    <row r="35">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6573,24 +6577,24 @@
         <v>95</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q35" s="2"/>
       <c r="R35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="S35" t="s" s="2">
         <v>83</v>
@@ -6632,7 +6636,7 @@
         <v>83</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6653,10 +6657,10 @@
         <v>83</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>83</v>
@@ -6667,10 +6671,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6696,14 +6700,14 @@
         <v>108</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>83</v>
@@ -6752,7 +6756,7 @@
         <v>83</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6773,10 +6777,10 @@
         <v>83</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>83</v>
@@ -6787,10 +6791,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6813,19 +6817,19 @@
         <v>95</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>83</v>
@@ -6874,7 +6878,7 @@
         <v>83</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6895,10 +6899,10 @@
         <v>83</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>83</v>
@@ -6909,10 +6913,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6938,16 +6942,16 @@
         <v>108</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>83</v>
@@ -6996,7 +7000,7 @@
         <v>83</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -7017,10 +7021,10 @@
         <v>83</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>83</v>
@@ -7029,16 +7033,16 @@
         <v>83</v>
       </c>
     </row>
-    <row r="39" hidden="true">
+    <row r="39">
       <c r="A39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
@@ -7057,19 +7061,19 @@
         <v>95</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>83</v>
@@ -7094,13 +7098,13 @@
         <v>83</v>
       </c>
       <c r="X39" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y39" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z39" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA39" t="s" s="2">
         <v>83</v>
@@ -7118,7 +7122,7 @@
         <v>83</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>94</v>
@@ -7133,30 +7137,30 @@
         <v>106</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7271,10 +7275,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7391,10 +7395,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7417,19 +7421,19 @@
         <v>95</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>83</v>
@@ -7466,7 +7470,7 @@
         <v>83</v>
       </c>
       <c r="AB42" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AC42" s="2"/>
       <c r="AD42" t="s" s="2">
@@ -7476,7 +7480,7 @@
         <v>121</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -7497,10 +7501,10 @@
         <v>83</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>83</v>
@@ -7511,13 +7515,13 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C43" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D43" t="s" s="2">
         <v>83</v>
@@ -7539,19 +7543,19 @@
         <v>95</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="O43" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>83</v>
@@ -7600,7 +7604,7 @@
         <v>83</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7621,10 +7625,10 @@
         <v>83</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="AO43" t="s" s="2">
         <v>83</v>
@@ -7635,10 +7639,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7753,10 +7757,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7873,10 +7877,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7902,23 +7906,23 @@
         <v>136</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q46" s="2"/>
       <c r="R46" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="S46" t="s" s="2">
         <v>83</v>
@@ -7960,7 +7964,7 @@
         <v>83</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7981,10 +7985,10 @@
         <v>83</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>83</v>
@@ -7995,10 +7999,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -8024,13 +8028,13 @@
         <v>108</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -8080,7 +8084,7 @@
         <v>83</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -8101,10 +8105,10 @@
         <v>83</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>83</v>
@@ -8115,10 +8119,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8141,24 +8145,24 @@
         <v>95</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q48" s="2"/>
       <c r="R48" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="S48" t="s" s="2">
         <v>83</v>
@@ -8200,7 +8204,7 @@
         <v>83</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -8221,10 +8225,10 @@
         <v>83</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>83</v>
@@ -8235,10 +8239,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8264,14 +8268,14 @@
         <v>108</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>83</v>
@@ -8320,7 +8324,7 @@
         <v>83</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>81</v>
@@ -8341,10 +8345,10 @@
         <v>83</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>83</v>
@@ -8355,10 +8359,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8381,19 +8385,19 @@
         <v>95</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>83</v>
@@ -8442,7 +8446,7 @@
         <v>83</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -8463,10 +8467,10 @@
         <v>83</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>83</v>
@@ -8477,10 +8481,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8506,16 +8510,16 @@
         <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O51" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>83</v>
@@ -8564,7 +8568,7 @@
         <v>83</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -8585,10 +8589,10 @@
         <v>83</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>83</v>
@@ -8597,12 +8601,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="52" hidden="true">
+    <row r="52">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8625,19 +8629,19 @@
         <v>95</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>83</v>
@@ -8686,7 +8690,7 @@
         <v>83</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8701,19 +8705,19 @@
         <v>106</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>83</v>
@@ -8721,10 +8725,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8747,16 +8751,16 @@
         <v>95</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8806,7 +8810,7 @@
         <v>83</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8827,13 +8831,13 @@
         <v>83</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>83</v>
@@ -8841,14 +8845,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8867,19 +8871,19 @@
         <v>95</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>83</v>
@@ -8928,7 +8932,7 @@
         <v>83</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8943,34 +8947,34 @@
         <v>106</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="55" hidden="true">
+    <row r="55">
       <c r="A55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8989,19 +8993,19 @@
         <v>95</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>83</v>
@@ -9050,7 +9054,7 @@
         <v>83</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -9059,25 +9063,25 @@
         <v>94</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AP55" t="s" s="2">
         <v>83</v>
@@ -9085,10 +9089,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -9114,13 +9118,13 @@
         <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -9170,7 +9174,7 @@
         <v>83</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -9191,13 +9195,13 @@
         <v>83</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>83</v>
@@ -9205,10 +9209,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9231,17 +9235,17 @@
         <v>95</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>83</v>
@@ -9290,7 +9294,7 @@
         <v>83</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -9305,19 +9309,19 @@
         <v>106</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>83</v>
@@ -9325,10 +9329,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9351,19 +9355,19 @@
         <v>95</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>83</v>
@@ -9400,17 +9404,17 @@
         <v>83</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AC58" s="2"/>
       <c r="AD58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -9419,7 +9423,7 @@
         <v>94</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AJ58" t="s" s="2">
         <v>106</v>
@@ -9428,30 +9432,30 @@
         <v>83</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="59" hidden="true">
+    <row r="59">
       <c r="A59" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D59" t="s" s="2">
         <v>83</v>
@@ -9473,19 +9477,19 @@
         <v>95</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>83</v>
@@ -9534,7 +9538,7 @@
         <v>83</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -9543,7 +9547,7 @@
         <v>94</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>106</v>
@@ -9552,27 +9556,27 @@
         <v>83</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP59" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9687,10 +9691,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9805,12 +9809,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="62" hidden="true">
+    <row r="62">
       <c r="A62" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9833,19 +9837,19 @@
         <v>95</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>83</v>
@@ -9894,7 +9898,7 @@
         <v>83</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9915,10 +9919,10 @@
         <v>83</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>83</v>
@@ -9929,10 +9933,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9955,23 +9959,23 @@
         <v>95</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="R63" t="s" s="2">
         <v>83</v>
@@ -9992,13 +9996,13 @@
         <v>83</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>83</v>
@@ -10016,7 +10020,7 @@
         <v>83</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -10037,10 +10041,10 @@
         <v>83</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AO63" t="s" s="2">
         <v>83</v>
@@ -10049,12 +10053,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="64" hidden="true">
+    <row r="64">
       <c r="A64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10080,14 +10084,14 @@
         <v>108</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>83</v>
@@ -10136,7 +10140,7 @@
         <v>83</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -10157,10 +10161,10 @@
         <v>83</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>83</v>
@@ -10169,12 +10173,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="65" hidden="true">
+    <row r="65">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10200,21 +10204,21 @@
         <v>136</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>83</v>
       </c>
       <c r="Q65" s="2"/>
       <c r="R65" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="S65" t="s" s="2">
         <v>83</v>
@@ -10256,7 +10260,7 @@
         <v>83</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -10265,7 +10269,7 @@
         <v>94</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AJ65" t="s" s="2">
         <v>106</v>
@@ -10277,10 +10281,10 @@
         <v>83</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>83</v>
@@ -10289,12 +10293,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="66" hidden="true">
+    <row r="66">
       <c r="A66" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10317,19 +10321,19 @@
         <v>95</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>83</v>
@@ -10354,13 +10358,13 @@
         <v>83</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>83</v>
@@ -10378,7 +10382,7 @@
         <v>83</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -10399,10 +10403,10 @@
         <v>83</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AO66" t="s" s="2">
         <v>83</v>
@@ -10411,12 +10415,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10439,19 +10443,19 @@
         <v>83</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="O67" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>83</v>
@@ -10476,13 +10480,13 @@
         <v>83</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y67" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z67" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>83</v>
@@ -10500,7 +10504,7 @@
         <v>83</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -10509,7 +10513,7 @@
         <v>94</v>
       </c>
       <c r="AI67" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ67" t="s" s="2">
         <v>106</v>
@@ -10521,10 +10525,10 @@
         <v>83</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO67" t="s" s="2">
         <v>83</v>
@@ -10535,14 +10539,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10561,19 +10565,19 @@
         <v>83</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>83</v>
@@ -10598,13 +10602,13 @@
         <v>83</v>
       </c>
       <c r="X68" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y68" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z68" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA68" t="s" s="2">
         <v>83</v>
@@ -10622,7 +10626,7 @@
         <v>83</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -10640,27 +10644,27 @@
         <v>83</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10683,19 +10687,19 @@
         <v>83</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="O69" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>83</v>
@@ -10744,7 +10748,7 @@
         <v>83</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10765,10 +10769,10 @@
         <v>83</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="AO69" t="s" s="2">
         <v>83</v>
@@ -10779,10 +10783,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10805,16 +10809,16 @@
         <v>83</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10840,13 +10844,13 @@
         <v>83</v>
       </c>
       <c r="X70" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y70" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="Z70" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="AA70" t="s" s="2">
         <v>83</v>
@@ -10864,7 +10868,7 @@
         <v>83</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10882,27 +10886,27 @@
         <v>83</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="AO70" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10925,19 +10929,19 @@
         <v>83</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>83</v>
@@ -10962,11 +10966,11 @@
         <v>83</v>
       </c>
       <c r="X71" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y71" s="2"/>
       <c r="Z71" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="AA71" t="s" s="2">
         <v>83</v>
@@ -10984,7 +10988,7 @@
         <v>83</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -11005,10 +11009,10 @@
         <v>83</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>83</v>
@@ -11019,10 +11023,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -11045,16 +11049,16 @@
         <v>83</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
@@ -11104,7 +11108,7 @@
         <v>83</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -11122,27 +11126,27 @@
         <v>83</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11165,16 +11169,16 @@
         <v>83</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -11224,7 +11228,7 @@
         <v>83</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -11242,27 +11246,27 @@
         <v>83</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11285,19 +11289,19 @@
         <v>83</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>83</v>
@@ -11346,7 +11350,7 @@
         <v>83</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -11358,7 +11362,7 @@
         <v>83</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>83</v>
@@ -11367,10 +11371,10 @@
         <v>83</v>
       </c>
       <c r="AM74" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>83</v>
@@ -11381,10 +11385,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11499,10 +11503,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11619,14 +11623,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11648,16 +11652,16 @@
         <v>115</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>83</v>
@@ -11706,7 +11710,7 @@
         <v>83</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -11730,7 +11734,7 @@
         <v>83</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>83</v>
@@ -11741,10 +11745,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11767,13 +11771,13 @@
         <v>83</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
@@ -11824,7 +11828,7 @@
         <v>83</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11833,7 +11837,7 @@
         <v>94</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>106</v>
@@ -11845,10 +11849,10 @@
         <v>83</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>83</v>
@@ -11859,10 +11863,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11885,13 +11889,13 @@
         <v>83</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11942,7 +11946,7 @@
         <v>83</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11951,7 +11955,7 @@
         <v>94</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>106</v>
@@ -11963,10 +11967,10 @@
         <v>83</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>83</v>
@@ -11977,10 +11981,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -12003,19 +12007,19 @@
         <v>83</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>83</v>
@@ -12040,13 +12044,13 @@
         <v>83</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>83</v>
@@ -12064,7 +12068,7 @@
         <v>83</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>81</v>
@@ -12082,13 +12086,13 @@
         <v>83</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>83</v>
@@ -12099,10 +12103,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12125,19 +12129,19 @@
         <v>83</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>83</v>
@@ -12162,13 +12166,13 @@
         <v>83</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y81" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="Z81" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>83</v>
@@ -12186,7 +12190,7 @@
         <v>83</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -12204,13 +12208,13 @@
         <v>83</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>83</v>
@@ -12221,10 +12225,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12247,17 +12251,17 @@
         <v>83</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>83</v>
@@ -12306,7 +12310,7 @@
         <v>83</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -12330,7 +12334,7 @@
         <v>83</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AO82" t="s" s="2">
         <v>83</v>
@@ -12341,10 +12345,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12370,10 +12374,10 @@
         <v>108</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12424,7 +12428,7 @@
         <v>83</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -12445,10 +12449,10 @@
         <v>83</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>83</v>
@@ -12459,10 +12463,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12485,16 +12489,16 @@
         <v>95</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12544,7 +12548,7 @@
         <v>83</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -12565,10 +12569,10 @@
         <v>83</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="AO84" t="s" s="2">
         <v>83</v>
@@ -12579,10 +12583,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12605,16 +12609,16 @@
         <v>95</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12664,7 +12668,7 @@
         <v>83</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -12685,10 +12689,10 @@
         <v>83</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="AO85" t="s" s="2">
         <v>83</v>
@@ -12697,12 +12701,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="86" hidden="true">
+    <row r="86">
       <c r="A86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12725,19 +12729,19 @@
         <v>95</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>83</v>
@@ -12786,7 +12790,7 @@
         <v>83</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -12798,7 +12802,7 @@
         <v>83</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>83</v>
@@ -12807,10 +12811,10 @@
         <v>83</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="AO86" t="s" s="2">
         <v>83</v>
@@ -12821,10 +12825,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12939,10 +12943,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -13059,14 +13063,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13088,16 +13092,16 @@
         <v>115</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>118</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>83</v>
@@ -13146,7 +13150,7 @@
         <v>83</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>81</v>
@@ -13170,7 +13174,7 @@
         <v>83</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>83</v>
@@ -13179,12 +13183,12 @@
         <v>83</v>
       </c>
     </row>
-    <row r="90" hidden="true">
+    <row r="90">
       <c r="A90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13207,19 +13211,19 @@
         <v>95</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>83</v>
@@ -13244,13 +13248,13 @@
         <v>83</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>83</v>
@@ -13268,7 +13272,7 @@
         <v>83</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>94</v>
@@ -13286,27 +13290,27 @@
         <v>83</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="AM90" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>83</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13329,19 +13333,19 @@
         <v>95</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>83</v>
@@ -13366,13 +13370,13 @@
         <v>83</v>
       </c>
       <c r="X91" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y91" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="Z91" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="AA91" t="s" s="2">
         <v>83</v>
@@ -13390,7 +13394,7 @@
         <v>83</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -13399,7 +13403,7 @@
         <v>94</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="AJ91" t="s" s="2">
         <v>106</v>
@@ -13408,27 +13412,27 @@
         <v>83</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP91" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
     </row>
-    <row r="92" hidden="true">
+    <row r="92">
       <c r="A92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13451,19 +13455,19 @@
         <v>83</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>83</v>
@@ -13488,13 +13492,13 @@
         <v>83</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>83</v>
@@ -13512,7 +13516,7 @@
         <v>83</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -13521,7 +13525,7 @@
         <v>94</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>106</v>
@@ -13533,10 +13537,10 @@
         <v>83</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="AO92" t="s" s="2">
         <v>83</v>
@@ -13547,14 +13551,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13573,19 +13577,19 @@
         <v>83</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>83</v>
@@ -13610,13 +13614,13 @@
         <v>83</v>
       </c>
       <c r="X93" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Y93" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="Z93" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AA93" t="s" s="2">
         <v>83</v>
@@ -13634,7 +13638,7 @@
         <v>83</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -13652,27 +13656,27 @@
         <v>83</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="AO93" t="s" s="2">
         <v>83</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13698,16 +13702,16 @@
         <v>84</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>83</v>
@@ -13756,7 +13760,7 @@
         <v>83</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -13777,10 +13781,10 @@
         <v>83</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO94" t="s" s="2">
         <v>83</v>
@@ -13791,12 +13795,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AP94">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
